--- a/site/Dayforce-to-ServiceNow-Data-Synchronization/headings.xlsx
+++ b/site/Dayforce-to-ServiceNow-Data-Synchronization/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,51 +441,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Key Features</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>h_01J70BR39BAVVVV4MTDG7T04J6</t>
+          <t>h_01KK95MYJTZ591DNFY0C6J62EB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01J70BR39BAVVVV4MTDG7T04J6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYJTZ591DNFY0C6J62EB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Ticket Generation Workflow</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>h_01KK95MYJVTYBM2FV360G1R4DT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYJVTYBM2FV360G1R4DT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,217 +495,217 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01KK95MYJYFA0R5D2HQXS7D76W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYJYFA0R5D2HQXS7D76W</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01KK95MYK0BNZ4JWW70Y0RDQ40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYK0BNZ4JWW70Y0RDQ40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01JZSCGEFJCNXA1605VDMS55X8</t>
+          <t>h_01KK95MYK14Z1ZQXW2FNVNHM2N</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#01JZSCGEFJCNXA1605VDMS55X8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYK14Z1ZQXW2FNVNHM2N</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Integration Scenarios</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01K7GW1R7W9N6NFT0NF4WD92RB</t>
+          <t>h_01KK95MYK31D267KWG7302ZG8E</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K7GW1R7W9N6NFT0NF4WD92RB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYK31D267KWG7302ZG8E</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Execution Features</t>
+          <t>Integration Scenarios</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01K7GW1Z46TZ5SC32RNXZNDWBY</t>
+          <t>h_01KK95MYK3EA2TX2Q5X95X2994</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K7GW1Z46TZ5SC32RNXZNDWBY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYK3EA2TX2Q5X95X2994</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Onboarding Tickets Generation</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01K7HN40EZC066WVMMQBXW6M3Q</t>
+          <t>h_01KK95MYK41BEWB4GT384JQQH1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K7HN40EZC066WVMMQBXW6M3Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYK41BEWB4GT384JQQH1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Offboarding Tickets Generation</t>
+          <t>Manage Tickets</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01K7HN40EZZSAGG32F6RBK41ET</t>
+          <t>h_01KK95MYK6M2SB1PHC9RTKBFZQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K7HN40EZZSAGG32F6RBK41ET</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYK6M2SB1PHC9RTKBFZQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Departments Sync</t>
+          <t>Manage Departments</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01K7HMJDHFEX4XYSWC0BBW6XXT</t>
+          <t>h_01KK95PP363NBECF8RKE9JF657</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K7HMJDHFEX4XYSWC0BBW6XXT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95PP363NBECF8RKE9JF657</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Locations Sync</t>
+          <t>Manage Locations</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K7HP6V385SYANKC21JV3XYZW</t>
+          <t>h_01KK95MYKWA6EMK05VTBG6XZA7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K7HP6V385SYANKC21JV3XYZW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYKWA6EMK05VTBG6XZA7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Users Sync</t>
+          <t>Manage Users</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K7HRB286245R12W0DCCHAWTP</t>
+          <t>h_01KK95MYM1V0CR47JP90R8Y3QE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K7HRB286245R12W0DCCHAWTP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM1V0CR47JP90R8Y3QE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sample Ticket Description Template</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,100 +715,232 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01JY5VVTJHHVSKTS2X4BEFRJV8</t>
+          <t>h_01KK95MYM5XGH9ZAWPWV432X0Q</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01JY5VVTJHHVSKTS2X4BEFRJV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM5XGH9ZAWPWV432X0Q</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Dayforce Department Debug Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>h_01KK95MYM68YZAMJ07Z39SPJTJ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM68YZAMJ07Z39SPJTJ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Dayforce Location Debug Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KK95MYM658C9916EQP9AXREF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM658C9916EQP9AXREF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Dayforce Job Family Debug Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KK95MYM7JYTSPAA0JAXE74F0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM7JYTSPAA0JAXE74F0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KK95MYM831WSX2H7B7J1A7EX</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM831WSX2H7B7J1A7EX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KK95MYM9CH849QAYDSBA3R26</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM9CH849QAYDSBA3R26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sample Ticket Description Template</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KK95VBWTFQ0QRYA46J3FD1HW</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95VBWTFQ0QRYA46J3FD1HW</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KK95SA2QRFTDZDNVE7TBMK5P</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95SA2QRFTDZDNVE7TBMK5P</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KK95MYMABMK6JZ9Q03EE68E7</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMABMK6JZ9Q03EE68E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KK95MYMASAB0J2T6V8G6HY01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMASAB0J2T6V8G6HY01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KK95MYMA06SGMX801HXHX4H7</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMA06SGMX801HXHX4H7</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-ServiceNow-Data-Synchronization/headings.xlsx
+++ b/site/Dayforce-to-ServiceNow-Data-Synchronization/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manage Departments</t>
+          <t>Manage Job Families</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KK95PP363NBECF8RKE9JF657</t>
+          <t>h_01KKB2ZE8HZTP6B1FZA7GTM8V8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95PP363NBECF8RKE9JF657</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KKB2ZE8HZTP6B1FZA7GTM8V8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Locations</t>
+          <t>Manage Departments</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KK95MYKWA6EMK05VTBG6XZA7</t>
+          <t>h_01KK95PP363NBECF8RKE9JF657</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYKWA6EMK05VTBG6XZA7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95PP363NBECF8RKE9JF657</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Users</t>
+          <t>Manage Locations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KK95MYM1V0CR47JP90R8Y3QE</t>
+          <t>h_01KK95MYKWA6EMK05VTBG6XZA7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM1V0CR47JP90R8Y3QE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYKWA6EMK05VTBG6XZA7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Manage Users</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KK95MYM5XGH9ZAWPWV432X0Q</t>
+          <t>h_01KK95MYM1V0CR47JP90R8Y3QE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM5XGH9ZAWPWV432X0Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM1V0CR47JP90R8Y3QE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dayforce Department Debug Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KK95MYM68YZAMJ07Z39SPJTJ</t>
+          <t>h_01KK95MYM5XGH9ZAWPWV432X0Q</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM68YZAMJ07Z39SPJTJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM5XGH9ZAWPWV432X0Q</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dayforce Location Debug Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KK95MYM658C9916EQP9AXREF</t>
+          <t>h_01KK95MYM831WSX2H7B7J1A7EX</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM658C9916EQP9AXREF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM831WSX2H7B7J1A7EX</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dayforce Job Family Debug Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KK95MYM7JYTSPAA0JAXE74F0</t>
+          <t>h_01KK95MYM9CH849QAYDSBA3R26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM7JYTSPAA0JAXE74F0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM9CH849QAYDSBA3R26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Sample Ticket Description Template</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,142 +803,98 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KK95MYM831WSX2H7B7J1A7EX</t>
+          <t>h_01KK95VBWTFQ0QRYA46J3FD1HW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM831WSX2H7B7J1A7EX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95VBWTFQ0QRYA46J3FD1HW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KK95MYM9CH849QAYDSBA3R26</t>
+          <t>h_01KK95SA2QRFTDZDNVE7TBMK5P</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYM9CH849QAYDSBA3R26</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95SA2QRFTDZDNVE7TBMK5P</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sample Ticket Description Template</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KK95VBWTFQ0QRYA46J3FD1HW</t>
+          <t>h_01KK95MYMABMK6JZ9Q03EE68E7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95VBWTFQ0QRYA46J3FD1HW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMABMK6JZ9Q03EE68E7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KK95SA2QRFTDZDNVE7TBMK5P</t>
+          <t>h_01KK95MYMASAB0J2T6V8G6HY01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95SA2QRFTDZDNVE7TBMK5P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMASAB0J2T6V8G6HY01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KK95MYMABMK6JZ9Q03EE68E7</t>
+          <t>h_01KK95MYMA06SGMX801HXHX4H7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMABMK6JZ9Q03EE68E7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>h_01KK95MYMASAB0J2T6V8G6HY01</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMASAB0J2T6V8G6HY01</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_01KK95MYMA06SGMX801HXHX4H7</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-ServiceNow-Data-Synchronization/#h_01KK95MYMA06SGMX801HXHX4H7</t>
         </is>
